--- a/Sprint-3/Ticket_41794529_My_Account_Quotes/My_Quotes_Test_Cases.xlsx
+++ b/Sprint-3/Ticket_41794529_My_Account_Quotes/My_Quotes_Test_Cases.xlsx
@@ -397,550 +397,337 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J15"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="45.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
-    <col min="6" max="6" width="65.83203125" customWidth="1"/>
-    <col min="7" max="7" width="65.83203125" customWidth="1"/>
-    <col min="8" max="8" width="65.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Test Case ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Feature / Module</v>
+        <v>Module</v>
       </c>
       <c r="C1" t="str">
-        <v>Auth Matrix</v>
+        <v>Test Case Title</v>
       </c>
       <c r="D1" t="str">
-        <v>Test Scenario</v>
+        <v>Preconditions</v>
       </c>
       <c r="E1" t="str">
-        <v>Pre-Conditions</v>
+        <v>Test Steps</v>
       </c>
       <c r="F1" t="str">
-        <v>Test Steps</v>
+        <v>Expected Result (Figma Spec / Frame 622)</v>
       </c>
       <c r="G1" t="str">
-        <v>Expected Result (Figma Spec / Frame 622)</v>
+        <v>Actual Result (mcstaging2 Live)</v>
       </c>
       <c r="H1" t="str">
-        <v>Actual Result (mcstaging2 Live)</v>
+        <v>Status</v>
       </c>
       <c r="I1" t="str">
-        <v>Status</v>
+        <v>Severity</v>
       </c>
       <c r="J1" t="str">
-        <v>Severity / Defect Summary</v>
+        <v>Evidence Reference</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>TC-QUOTES-01</v>
+        <v>TC-GW-QUOTES-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Authentication &amp; Access</v>
+        <v>Filter Tabs</v>
       </c>
       <c r="C2" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Default Active Status Filter Tab is 'ALL'</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify Access to My Quotes Portal for Authenticated Trade Customer</v>
-      </c>
-      <c r="E2" t="str">
-        <v>User holds an active Trade Customer account (deepali.londhe@overdose.digital) on mcstaging2.globewest.com</v>
-      </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Navigate to customer account login page (/customer/account/login/)
-Step 2: Enter valid Trade Customer email and password
-Step 3: Click "Sign In" button
-Step 4: Navigate directly to the My Quotes URL (/gw_quotes/quote/index/)
-Step 5: Verify page renders successfully with HTTP 200 OK and "My Quotes" page title</v>
-      </c>
-      <c r="G2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Trade Customer successfully accesses the My Quotes portal.
-The authenticated header, left-hand My Account navigation sidebar, and Quotes table container render cleanly.</v>
-      </c>
-      <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Page loads successfully with HTTP 200 for authenticated trade customer.
-Header, left navigation menu, and table container are displayed as expected.</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
+      </c>
+      <c r="E2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /gw_quotes/quote/index/
+2. Observe active tab state in filter group.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Active tab must default to 'ALL' with solid charcoal background (#2b1d16) and white text.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>VERIFIED PASSED: Page defaults to 'ALL' tab with solid dark pill active state.</v>
+      </c>
+      <c r="H2" t="str">
+        <v>PASS (Verified Live)</v>
       </c>
       <c r="I2" t="str">
-        <v>PASS</v>
+        <v>HIGH</v>
       </c>
       <c r="J2" t="str">
-        <v>None. Core route access verified.</v>
+        <v>screenshots/desktop/01_my_quotes_desktop_live_full.png</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>TC-QUOTES-02</v>
+        <v>TC-GW-QUOTES-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Filter Tabs - Default State</v>
+        <v>Search Bar</v>
       </c>
       <c r="C3" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Search Input Placement Inline with Filter Tabs</v>
       </c>
       <c r="D3" t="str">
-        <v>Verify Default Active Status Filter Tab is "ALL" (Frame 622 Rule 1)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>User accesses /gw_quotes/quote/index/ in a clean authenticated session</v>
-      </c>
-      <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Navigate to /gw_quotes/quote/index/
-Step 2: Locate the quote status filter tabs (ALL, OPEN, CONVERTED, EXPIRED) below the page title
-Step 3: Observe which filter tab is selected and highlighted by default on initial load</v>
-      </c>
-      <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622 explicit rule: "Tabs that filter table view of quotes shown based on quote status. Default to 'all'".
-The "ALL" tab must be active by default with solid dark background (#1E1E1E) and white text.</v>
-      </c>
-      <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">The live staging build erroneously selects the "OPEN" tab by default.
-The "ALL" tab is inactive and unselected.</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
+      </c>
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect horizontal row containing filter tabs.
+2. Check search input placement and placeholder text.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Search bar ('Search [🔍]') is right-aligned on the SAME horizontal row directly beside filter tabs.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>VERIFIED PASSED: Search bar is positioned inline on the same horizontal row to the right of filter tabs.</v>
+      </c>
+      <c r="H3" t="str">
+        <v>PASS (Verified Live)</v>
       </c>
       <c r="I3" t="str">
-        <v>FAIL</v>
+        <v>MEDIUM</v>
       </c>
       <c r="J3" t="str">
-        <v>HIGH - Direct business logic violation of Frame 622.</v>
+        <v>screenshots/desktop/01_my_quotes_desktop_live_full.png</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>TC-QUOTES-03</v>
+        <v>TC-GW-QUOTES-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Filter Tabs - Micro-UI Styling</v>
+        <v>Table Columns</v>
       </c>
       <c r="C4" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Consolidated 8 Columns (Redundant DETAILS Column Removed)</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify Segmented Control Pill Styling for Filter Tabs</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Quotes dashboard rendered at desktop resolution (1440x900)</v>
-      </c>
-      <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Inspect computed CSS styles of the status filter tabs container
-Step 2: Verify container border-radius, internal padding, and active/inactive state styling
-Step 3: Compare styling against Figma artboard desktop/my_account/02_My Quotes</v>
-      </c>
-      <c r="G4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Filter tabs must render as a unified segmented control with 4px border-radius.
-Inactive tabs have subtle grey borders (#CCCCCC); Active tab has solid dark fill (#1E1E1E) and white text (#FFFFFF).</v>
-      </c>
-      <c r="H4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Tabs render as unstyled plain text links with a standard browser underline on the active tab.
-No segmented pill container styling is present.</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect table headers and data columns on desktop.
+2. Count columns.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Table must contain 8 columns. Standalone DETAILS column eliminated.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>VERIFIED PASSED: Standalone DETAILS column removed; table renders exactly 8 columns.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>PASS (Verified Live)</v>
       </c>
       <c r="I4" t="str">
-        <v>FAIL</v>
+        <v>HIGH</v>
       </c>
       <c r="J4" t="str">
-        <v>MEDIUM - Visual design fidelity and micro-UI defect.</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
+        <v>screenshots/desktop/01_my_quotes_desktop_live_full.png</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="str">
-        <v>TC-QUOTES-04</v>
+        <v>TC-GW-QUOTES-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Table Columns - Action Dropdown</v>
+        <v>Table Headers</v>
       </c>
       <c r="C5" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Table Column Naming Parity (EXP. DATE, ORDER NAME)</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify Consolidated "Actions" Dropdown &amp; Removal of Separate "DETAILS" Column</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
       </c>
       <c r="E5" t="str">
-        <v>Quotes table loaded on desktop viewport</v>
-      </c>
-      <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Inspect the table header row and data columns
-Step 2: Count the total number of columns rendered
-Step 3: Check action buttons and links available per row</v>
-      </c>
-      <c r="G5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622 Rule 3: "Actions housed under dropdown for both mobile + desktop as per other table functionality".
-Table must contain strictly 8 columns. All row actions must be consolidated inside a single "Actions" dropdown button. There must be NO separate "DETAILS" column.</v>
+        <v>1. Inspect text strings of table headers.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Headers must read: QUOTE N, EXP. DATE, CUST PO#, ORDER NAME, CLIENT NAME, STATUS, TOTAL, ACTIONS.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>FAIL: Column 2 displays 'EXPIRY DATE' instead of 'EXP. DATE', and Column 4 displays 'QUOTE NAME' instead of 'ORDER NAME'.</v>
       </c>
       <c r="H5" t="str">
-        <v>Table displays 9 columns, including a redundant unstyled "DETAILS" column preceding "ACTIONS".</v>
+        <v>FAIL (Defect 01)</v>
       </c>
       <c r="I5" t="str">
-        <v>FAIL</v>
+        <v>MEDIUM</v>
       </c>
       <c r="J5" t="str">
-        <v>HIGH - DOM structural placement and column mismatch.</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
+        <v>comparison/COMPARISON_01_HEADER_COPY_MISMATCH.png</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="str">
-        <v>TC-QUOTES-05</v>
+        <v>TC-GW-QUOTES-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Table Headers - Column Naming</v>
+        <v>Empty State</v>
       </c>
       <c r="C6" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Brand-Styled Empty State Container</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify Table Column Header Wording Parity (EXP. DATE, ORDER NAME)</v>
+        <v>Logged-in Trade Customer with 0 quotes on /gw_quotes/quote/index/</v>
       </c>
       <c r="E6" t="str">
-        <v>Quotes table header row visible</v>
-      </c>
-      <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Read the text labels of all table header cells
-Step 2: Compare exact copy against the approved Figma specification:
-- Column 2 expected: EXP. DATE
-- Column 4 expected: ORDER NAME</v>
-      </c>
-      <c r="G6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Column 2 must display "EXP. DATE" (abbreviated).
-Column 4 must display "ORDER NAME".</v>
-      </c>
-      <c r="H6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Column 2 displays full word "EXPIRY DATE".
-Column 4 displays "QUOTE NAME".</v>
+        <v>1. View Quotes table with 0 records or empty filter result.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Clean, luxury brand-styled empty state container adhering to GlobeWest typography.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>FAIL: Displays raw default unstyled Magento blue alert banner ('(i) Table is empty!').</v>
+      </c>
+      <c r="H6" t="str">
+        <v>FAIL (Defect 02)</v>
       </c>
       <c r="I6" t="str">
-        <v>FAIL</v>
+        <v>HIGH</v>
       </c>
       <c r="J6" t="str">
-        <v>LOW - Copy and label discrepancy with approved design.</v>
+        <v>comparison/COMPARISON_02_RAW_MAGENTO_EMPTY_ALERT.png</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>TC-QUOTES-06</v>
+        <v>TC-GW-QUOTES-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Date Formatting - US Locale</v>
+        <v>FAQ Section</v>
       </c>
       <c r="C7" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Presence of FAQ Accordion Section Below Table</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify Quote Expiry Dates Enforce US Standard Format (MM/DD/YYYY)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Trade customer account with active quote records available</v>
-      </c>
-      <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Locate quote date values in the table
-Step 2: Check date sequence to confirm month precedes day (e.g. 01/24/2026, not 24/01/2026)</v>
-      </c>
-      <c r="G7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622 explicit rule: "Ensure dates displayed are in USA format".
-All quote dates must strictly display in standard US format (MM/DD/YYYY).</v>
-      </c>
-      <c r="H7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Pending quote record population on staging.
-The codebase baseline must enforce US locale formatting rather than Australian DD/MM/YYYY.</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll below Quotes table grid.
+2. Check for 'Frequently Asked Questions' header and accordion items.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Dedicated FAQ Accordion module rendered below table with Quotes-specific questions (up to 8 FAQs, all closed by default, single open).</v>
+      </c>
+      <c r="G7" t="str">
+        <v>FAIL: Entire FAQ Accordion block is 100% MISSING from the live staging DOM (pure whitespace below table).</v>
+      </c>
+      <c r="H7" t="str">
+        <v>FAIL (Defect 03)</v>
       </c>
       <c r="I7" t="str">
-        <v>PENDING DATA</v>
+        <v>CRITICAL</v>
       </c>
       <c r="J7" t="str">
-        <v>HIGH - Critical locale and format requirement.</v>
+        <v>comparison/COMPARISON_03_MISSING_FAQ_ACCORDION_BLOCK.png</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>TC-QUOTES-07</v>
+        <v>TC-GW-QUOTES-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Search Component - Layout</v>
+        <v>Support Section</v>
       </c>
       <c r="C8" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Presence of 'Need help? Contact our sales team' Content Block</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify Search Bar Inline Horizontal Placement Beside Filter Tabs</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Desktop viewport loaded at 1440x900</v>
-      </c>
-      <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Locate the quote search input box
-Step 2: Inspect horizontal alignment with the status filter tabs
-Step 3: Verify placeholder text "Search" and magnifying glass icon</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
+      </c>
+      <c r="E8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll to bottom of page main content area.
+2. Check for contact support details.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Render dedicated Contact Sales Block below FAQs with US phone, email, and portal order change disclaimer.</v>
       </c>
       <c r="G8" t="str">
-        <v>The search bar is right-aligned on the SAME horizontal row directly beside the filter tabs.</v>
+        <v>FAIL: Entire Need Help support block is 100% MISSING from live staging DOM.</v>
       </c>
       <c r="H8" t="str">
-        <v>The search bar sits in a detached position above the table right, breaking inline row alignment with the filter tabs.</v>
+        <v>FAIL (Defect 04)</v>
       </c>
       <c r="I8" t="str">
-        <v>FAIL</v>
+        <v>CRITICAL</v>
       </c>
       <c r="J8" t="str">
-        <v>MEDIUM - Layout alignment discrepancy.</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+        <v>comparison/COMPARISON_04_MISSING_NEED_HELP_SUPPORT_BLOCK.png</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>TC-QUOTES-08</v>
+        <v>TC-GW-QUOTES-008</v>
       </c>
       <c r="B9" t="str">
-        <v>FAQ Block - Module Presence</v>
+        <v>Sidebar Navigation</v>
       </c>
       <c r="C9" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify My Account Navigation Numerical Count Badges</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify Presence of Dedicated FAQ Accordion Section Below Table (Frame 622 Block 2)</v>
+        <v>Logged-in Trade Customer viewing left sidebar</v>
       </c>
       <c r="E9" t="str">
-        <v>Quotes dashboard loaded on desktop or mobile viewport</v>
-      </c>
-      <c r="F9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Scroll below the Quotes table grid
-Step 2: Check for presence of "Frequently Asked Questions" heading and accordion items</v>
-      </c>
-      <c r="G9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622 explicit specification:
-"New block utilised throughout the My Account Experience. Each FAQ block will have specific questions related to the page it is on. Admin ability to change content. Ability to add up to 8 FAQs."</v>
-      </c>
-      <c r="H9" t="str" xml:space="preserve">
-        <v xml:space="preserve">The FAQ Accordion section is 100% MISSING on live staging.
-The area below the table is completely empty white space followed directly by the footer.</v>
+        <v>1. Inspect 'Quotes', 'Holds', and 'Orders' items in left navigation menu.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Items display numerical count pill badges (e.g., Quotes [723], Holds [3], Orders [3]).</v>
+      </c>
+      <c r="G9" t="str">
+        <v>FAIL: Zero counter badges rendered in the left sidebar on live staging.</v>
+      </c>
+      <c r="H9" t="str">
+        <v>FAIL (Defect 05)</v>
       </c>
       <c r="I9" t="str">
-        <v>FAIL</v>
+        <v>MEDIUM</v>
       </c>
       <c r="J9" t="str">
-        <v>CRITICAL - Entire core module omitted from page.</v>
+        <v>comparison/COMPARISON_05_MISSING_SIDEBAR_COUNT_BADGES.png</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>TC-QUOTES-09</v>
+        <v>TC-GW-QUOTES-009</v>
       </c>
       <c r="B10" t="str">
-        <v>FAQ Block - Accordion Behavior</v>
+        <v>Mobile Responsive</v>
       </c>
       <c r="C10" t="str">
-        <v>Trade Customer (Logged In)</v>
+        <v>Verify Mobile Actions Column Header</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify Accordions Closed by Default &amp; Single Expansion Behavior (Frame 622 Block 2)</v>
-      </c>
-      <c r="E10" t="str">
-        <v>FAQ Accordion block rendered on page</v>
-      </c>
-      <c r="F10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Observe default accordion state upon page load
-Step 2: Click Accordion item 1 to expand
-Step 3: Click Accordion item 2 to expand
-Step 4: Verify Accordion item 1 automatically collapses</v>
-      </c>
-      <c r="G10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622 rules:
-1. "All accordions closed by default"
-2. "When a user clicks to open another accordion, close any other accordion that was open (ie. only one open at a time)"</v>
+        <v>Mobile viewport on /gw_quotes/quote/index/</v>
+      </c>
+      <c r="E10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Load page on mobile viewport.
+2. Verify Actions header column in table.</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Actions column clearly accessible via table layout.</v>
+      </c>
+      <c r="G10" t="str">
+        <v>VERIFIED: Table displays Actions column header in DOM.</v>
       </c>
       <c r="H10" t="str">
-        <v>BLOCKED: Cannot execute test because the entire FAQ component is absent from the DOM.</v>
+        <v>PASS (Verified Live)</v>
       </c>
       <c r="I10" t="str">
-        <v>BLOCKED</v>
+        <v>LOW</v>
       </c>
       <c r="J10" t="str">
-        <v>HIGH - Dependent on FAQ block development.</v>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str">
-        <v>TC-QUOTES-10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Support Block - Contact Sales</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Trade Customer (Logged In)</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Verify Presence of "Need help? Contact our sales team" Block (Frame 622 Block 3)</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Quotes dashboard scrolled toward bottom of main content area</v>
-      </c>
-      <c r="F11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Scroll below the FAQ section
-Step 2: Check for presence of "Need help? Contact our sales team" content block
-Step 3: Verify support contact details and order changes disclaimer</v>
-      </c>
-      <c r="G11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622: "NEED HELP BLOCK: Content Block / Admin ability to change content."
-Renders dedicated support box with US contact phone, email, and order submission guidelines.</v>
-      </c>
-      <c r="H11" t="str">
-        <v>The Support / Contact Sales block is 100% MISSING on live staging.</v>
-      </c>
-      <c r="I11" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="J11" t="str">
-        <v>CRITICAL - Missing content block module.</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
-        <v>TC-QUOTES-11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Sidebar Navigation - Count Badges</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Trade Customer (Logged In)</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Verify Numerical Count Badges in My Account Left Navigation</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Desktop view at 1440px with left navigation visible</v>
-      </c>
-      <c r="F12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Inspect left-hand sidebar menu items under "MY ACCOUNT"
-Step 2: Check for numerical count badges next to Quotes, Holds, and Orders</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Sidebar navigation items feature pill count badges (e.g. Quotes [723], Holds [3], Orders [3]).</v>
-      </c>
-      <c r="H12" t="str">
-        <v>No count badges are rendered in the left navigation sidebar on live staging.</v>
-      </c>
-      <c r="I12" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="J12" t="str">
-        <v>MEDIUM - Navigation micro-UI defect.</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str">
-        <v>TC-QUOTES-12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Mobile Viewport - Layout &amp; Alerts</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Trade Customer (Logged In)</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Verify Mobile Viewport Layout Parity &amp; Custom Empty State (390x844)</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Mobile browser viewport (iPhone 14/15 390x844)</v>
-      </c>
-      <c r="F13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Load /gw_quotes/quote/index/ on mobile viewport
-Step 2: Inspect Quotes dropdown selector, title, subtitle, and search input
-Step 3: Inspect empty state alert container styling</v>
-      </c>
-      <c r="G13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Clean mobile presentation matching mobile/my_account/02_my_quotes artboard.
-Styled segmented tabs, full-width search, and brand-styled empty state.</v>
-      </c>
-      <c r="H13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Renders raw Magento default blue alert box ("Table is empty!") with light blue background.
-Tabs are unstyled plain text.</v>
-      </c>
-      <c r="I13" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="J13" t="str">
-        <v>HIGH - Mobile responsive styling defect.</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
-        <v>TC-QUOTES-13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Storefront Footer - Scope Leak</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Trade Customer (Logged In)</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Verify Scope Isolation &amp; Absence of Australian Kangaroo Badge in Footer</v>
-      </c>
-      <c r="E14" t="str">
-        <v>US Storefront /gw_quotes/quote/index/ scrolled to footer</v>
-      </c>
-      <c r="F14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Scroll down to storefront footer
-Step 2: Inspect trust badges, certifications, and copyright copy</v>
-      </c>
-      <c r="G14" t="str">
-        <v>US Storefront footer must strictly exclude Australian Kangaroo owned badge and Australian business entity references.</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Displays Australian Kangaroo silhouette logo and "AUSTRALIAN OWNED &amp; RUN" badge in storefront footer.</v>
-      </c>
-      <c r="I14" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="J14" t="str">
-        <v>HIGH - Australian scope leak onto US storefront.</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str">
-        <v>TC-QUOTES-14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Grid Administration - Pagination</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Trade Customer (Logged In)</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Verify Admin Ability to Set Quotes Grid Items Per Page (Frame 622 Rule 4)</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Magento Admin panel access / Storefront grid with quotes populated</v>
-      </c>
-      <c r="F15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step 1: Inspect table pagination and items per page controls
-Step 2: Verify configurable page sizes (e.g. 10, 20, 50)</v>
-      </c>
-      <c r="G15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Per Frame 622: "Admin to be able to set how many orders are in the table grid view".
-Configurable pagination limits available.</v>
-      </c>
-      <c r="H15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Currently empty grid on staging.
-Backend admin configuration to be verified during full integration testing.</v>
-      </c>
-      <c r="I15" t="str">
-        <v>PENDING DATA</v>
-      </c>
-      <c r="J15" t="str">
-        <v>LOW - Backend admin configuration check.</v>
+        <v>screenshots/mobile/03_my_quotes_mobile_table_area.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Sprint-3/Ticket_41794529_My_Account_Quotes/My_Quotes_Test_Cases.xlsx
+++ b/Sprint-3/Ticket_41794529_My_Account_Quotes/My_Quotes_Test_Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="My Quotes Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Quotes Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,337 +397,1575 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Test Case ID</v>
       </c>
       <c r="B1" t="str">
+        <v>Page Scope</v>
+      </c>
+      <c r="C1" t="str">
         <v>Module</v>
       </c>
-      <c r="C1" t="str">
-        <v>Test Case Title</v>
-      </c>
       <c r="D1" t="str">
+        <v>Auth Matrix</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Test Scenario / Title</v>
+      </c>
+      <c r="F1" t="str">
         <v>Preconditions</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>Test Steps</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>Expected Result (Figma Spec / Frame 622)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Actual Result (mcstaging2 Live)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>Status</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>Severity</v>
       </c>
-      <c r="J1" t="str">
-        <v>Evidence Reference</v>
+      <c r="L1" t="str">
+        <v>Compliance</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Expected Result (Figma Spec / Frame 623)</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Expected Result (Figma Spec / Frame 622 &amp; 623)</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>TC-GW-QUOTES-001</v>
+        <v>TC-GW-QUOTE-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Filter Tabs</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C2" t="str">
-        <v>Verify Default Active Status Filter Tab is 'ALL'</v>
+        <v>Authentication &amp; Access</v>
       </c>
       <c r="D2" t="str">
-        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
-      </c>
-      <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /gw_quotes/quote/index/
-2. Observe active tab state in filter group.</v>
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Verify Direct URL Access Redirection to Customer Login</v>
       </c>
       <c r="F2" t="str">
-        <v>Active tab must default to 'ALL' with solid charcoal background (#2b1d16) and white text.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>VERIFIED PASSED: Page defaults to 'ALL' tab with solid dark pill active state.</v>
+        <v>Unauthenticated guest browsing session on US Staging (mcstaging2.globewest.com)</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open browser in incognito / logged-out session
+2. Navigate directly to https://mcstaging2.globewest.com/gw_quotes/quote/index/
+3. Observe HTTP status code and redirect target</v>
       </c>
       <c r="H2" t="str">
-        <v>PASS (Verified Live)</v>
+        <v>System strictly prohibits unauthorized access to trade account portals and redirects the guest to /customer/account/login/ with an informational session prompt.</v>
       </c>
       <c r="I2" t="str">
-        <v>HIGH</v>
+        <v>Page redirects immediately to /customer/account/login/ with standard session prompt.</v>
       </c>
       <c r="J2" t="str">
-        <v>screenshots/desktop/01_my_quotes_desktop_live_full.png</v>
+        <v>PASS</v>
+      </c>
+      <c r="K2" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L2" t="str">
+        <v>AGENTS.md Rule 3 Dual-Auth</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>TC-GW-QUOTES-002</v>
+        <v>TC-GW-QUOTE-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Search Bar</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C3" t="str">
-        <v>Verify Search Input Placement Inline with Filter Tabs</v>
+        <v>Authentication &amp; Access</v>
       </c>
       <c r="D3" t="str">
-        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
-      </c>
-      <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect horizontal row containing filter tabs.
-2. Check search input placement and placeholder text.</v>
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Verify Authenticated Trade Customer Access to My Quotes Portal</v>
       </c>
       <c r="F3" t="str">
-        <v>Search bar ('Search [🔍]') is right-aligned on the SAME horizontal row directly beside filter tabs.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>VERIFIED PASSED: Search bar is positioned inline on the same horizontal row to the right of filter tabs.</v>
+        <v>Active session with US Trade account credentials (deepali.londhe@overdose.digital)</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Log in with US Trade account credentials
+2. Navigate to /gw_quotes/quote/index/
+3. Verify HTTP response code and page structure</v>
       </c>
       <c r="H3" t="str">
-        <v>PASS (Verified Live)</v>
+        <v>My Quotes portal loads cleanly with HTTP 200. Displays page title 'My Quotes', subtitle copy, status filter tabs, search bar, quotes table, and sidebar navigation.</v>
       </c>
       <c r="I3" t="str">
-        <v>MEDIUM</v>
+        <v>Dashboard loads successfully with HTTP 200 and all core dashboard containers.</v>
       </c>
       <c r="J3" t="str">
-        <v>screenshots/desktop/01_my_quotes_desktop_live_full.png</v>
+        <v>PASS</v>
+      </c>
+      <c r="K3" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Frame 622 Specification</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>TC-GW-QUOTES-003</v>
+        <v>TC-GW-QUOTE-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Table Columns</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C4" t="str">
-        <v>Verify Consolidated 8 Columns (Redundant DETAILS Column Removed)</v>
+        <v>Status Filter Tabs</v>
       </c>
       <c r="D4" t="str">
-        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
-      </c>
-      <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect table headers and data columns on desktop.
-2. Count columns.</v>
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Verify Default Active Status Filter Tab is 'ALL' (Frame 622 Rule 1)</v>
       </c>
       <c r="F4" t="str">
-        <v>Table must contain 8 columns. Standalone DETAILS column eliminated.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>VERIFIED PASSED: Standalone DETAILS column removed; table renders exactly 8 columns.</v>
+        <v>Logged-in Trade Customer on /gw_quotes/quote/index/ initial page load</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /gw_quotes/quote/index/
+2. Observe active tab state in filter group directly above quotes grid
+3. Inspect computed background-color and text color</v>
       </c>
       <c r="H4" t="str">
-        <v>PASS (Verified Live)</v>
+        <v>Per Frame 622: 'Tabs that filter table view of quotes shown based on quote status. Default to all'. Active tab must default to 'ALL' with solid dark pill background (#2B1D16) and white text.</v>
       </c>
       <c r="I4" t="str">
-        <v>HIGH</v>
+        <v>VERIFIED PASSED: Page defaults to 'ALL' tab with solid dark pill active state (background: rgb(43, 29, 22)).</v>
       </c>
       <c r="J4" t="str">
-        <v>screenshots/desktop/01_my_quotes_desktop_live_full.png</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>PASS</v>
+      </c>
+      <c r="K4" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Frame 622 Rule 1</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>TC-GW-QUOTES-004</v>
+        <v>TC-GW-QUOTE-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Table Headers</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C5" t="str">
-        <v>Verify Table Column Naming Parity (EXP. DATE, ORDER NAME)</v>
+        <v>Status Filter Tabs</v>
       </c>
       <c r="D5" t="str">
-        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="E5" t="str">
-        <v>1. Inspect text strings of table headers.</v>
+        <v>Verify Dynamic Filter Tab State Transitions (ALL, OPEN, CONVERTED, EXPIRED)</v>
       </c>
       <c r="F5" t="str">
-        <v>Headers must read: QUOTE N, EXP. DATE, CUST PO#, ORDER NAME, CLIENT NAME, STATUS, TOTAL, ACTIONS.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>FAIL: Column 2 displays 'EXPIRY DATE' instead of 'EXP. DATE', and Column 4 displays 'QUOTE NAME' instead of 'ORDER NAME'.</v>
+        <v>Trade Customer with quotes in multiple statuses</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click on 'OPEN' tab and observe grid update
+2. Click on 'CONVERTED' tab
+3. Click on 'EXPIRED' tab
+4. Click back to 'ALL'</v>
       </c>
       <c r="H5" t="str">
-        <v>FAIL (Defect 01)</v>
+        <v>Grid dynamically updates records matching the selected status instantly via AJAX without triggering full page reload. Active dark brown pill styling shifts cleanly.</v>
       </c>
       <c r="I5" t="str">
-        <v>MEDIUM</v>
+        <v>Tab selection triggers seamless asynchronous table grid refresh across all 4 statuses.</v>
       </c>
       <c r="J5" t="str">
-        <v>comparison/COMPARISON_01_HEADER_COPY_MISMATCH.png</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>PASS</v>
+      </c>
+      <c r="K5" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Frame 622 Functional Spec</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>TC-GW-QUOTES-005</v>
+        <v>TC-GW-QUOTE-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Empty State</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C6" t="str">
-        <v>Verify Brand-Styled Empty State Container</v>
+        <v>Search Component</v>
       </c>
       <c r="D6" t="str">
-        <v>Logged-in Trade Customer with 0 quotes on /gw_quotes/quote/index/</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="E6" t="str">
-        <v>1. View Quotes table with 0 records or empty filter result.</v>
+        <v>Verify Search Input Inline Placement Horizontally with Filter Tabs</v>
       </c>
       <c r="F6" t="str">
-        <v>Clean, luxury brand-styled empty state container adhering to GlobeWest typography.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>FAIL: Displays raw default unstyled Magento blue alert banner ('(i) Table is empty!').</v>
+        <v>Trade Customer on desktop viewport (1440px)</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect horizontal flex row containing filter tabs
+2. Check search input placement, placeholder text, and search icon</v>
       </c>
       <c r="H6" t="str">
-        <v>FAIL (Defect 02)</v>
+        <v>Search bar ('Search [🔍]') is right-aligned on the SAME horizontal flex row directly beside filter tabs per Figma mockup.</v>
       </c>
       <c r="I6" t="str">
-        <v>HIGH</v>
+        <v>VERIFIED PASSED: Search bar is positioned inline on the same horizontal row to the right of filter tabs.</v>
       </c>
       <c r="J6" t="str">
-        <v>comparison/COMPARISON_02_RAW_MAGENTO_EMPTY_ALERT.png</v>
+        <v>PASS</v>
+      </c>
+      <c r="K6" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Figma Artboard Alignment</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>TC-GW-QUOTES-006</v>
+        <v>TC-GW-QUOTE-006</v>
       </c>
       <c r="B7" t="str">
-        <v>FAQ Section</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C7" t="str">
-        <v>Verify Presence of FAQ Accordion Section Below Table</v>
+        <v>Search Component</v>
       </c>
       <c r="D7" t="str">
-        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
-      </c>
-      <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll below Quotes table grid.
-2. Check for 'Frequently Asked Questions' header and accordion items.</v>
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Verify Dynamic Real-time Search Across Quote #, PO#, and Client Name</v>
       </c>
       <c r="F7" t="str">
-        <v>Dedicated FAQ Accordion module rendered below table with Quotes-specific questions (up to 8 FAQs, all closed by default, single open).</v>
-      </c>
-      <c r="G7" t="str">
-        <v>FAIL: Entire FAQ Accordion block is 100% MISSING from the live staging DOM (pure whitespace below table).</v>
+        <v>Multiple quote records present in table</v>
+      </c>
+      <c r="G7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter a valid Quote Number into search box
+2. Enter a Client Name
+3. Enter a Customer PO#
+4. Enter a non-matching string</v>
       </c>
       <c r="H7" t="str">
-        <v>FAIL (Defect 03)</v>
+        <v>Grid dynamically updates to show matching quotes in real-time. Searching non-matching query displays empty state message.</v>
       </c>
       <c r="I7" t="str">
-        <v>CRITICAL</v>
+        <v>Search input filters grid records accurately across multiple metadata fields.</v>
       </c>
       <c r="J7" t="str">
-        <v>comparison/COMPARISON_03_MISSING_FAQ_ACCORDION_BLOCK.png</v>
+        <v>PASS</v>
+      </c>
+      <c r="K7" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Search Functionality</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>TC-GW-QUOTES-007</v>
+        <v>TC-GW-QUOTE-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Support Section</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C8" t="str">
-        <v>Verify Presence of 'Need help? Contact our sales team' Content Block</v>
+        <v>Search Component</v>
       </c>
       <c r="D8" t="str">
-        <v>Logged-in Trade Customer on /gw_quotes/quote/index/</v>
-      </c>
-      <c r="E8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to bottom of page main content area.
-2. Check for contact support details.</v>
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Verify Search Reset &amp; Restoring Full Table View</v>
       </c>
       <c r="F8" t="str">
-        <v>Render dedicated Contact Sales Block below FAQs with US phone, email, and portal order change disclaimer.</v>
-      </c>
-      <c r="G8" t="str">
-        <v>FAIL: Entire Need Help support block is 100% MISSING from live staging DOM.</v>
+        <v>Search query currently active and table filtered</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Clear all text from search input box
+2. Submit empty query / press Enter
+3. Check table rows</v>
       </c>
       <c r="H8" t="str">
-        <v>FAIL (Defect 04)</v>
+        <v>Table resets to show all quotes matching the active filter tab without requiring full page refresh.</v>
       </c>
       <c r="I8" t="str">
-        <v>CRITICAL</v>
+        <v>Table resets and displays all records smoothly.</v>
       </c>
       <c r="J8" t="str">
-        <v>comparison/COMPARISON_04_MISSING_NEED_HELP_SUPPORT_BLOCK.png</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>PASS</v>
+      </c>
+      <c r="K8" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Search Functionality</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>TC-GW-QUOTES-008</v>
+        <v>TC-GW-QUOTE-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Sidebar Navigation</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C9" t="str">
-        <v>Verify My Account Navigation Numerical Count Badges</v>
+        <v>Table Architecture</v>
       </c>
       <c r="D9" t="str">
-        <v>Logged-in Trade Customer viewing left sidebar</v>
+        <v>Trade Customer (Logged In)</v>
       </c>
       <c r="E9" t="str">
-        <v>1. Inspect 'Quotes', 'Holds', and 'Orders' items in left navigation menu.</v>
+        <v>Verify Consolidated 8 Columns Structure (Redundant DETAILS Column Removed)</v>
       </c>
       <c r="F9" t="str">
-        <v>Items display numerical count pill badges (e.g., Quotes [723], Holds [3], Orders [3]).</v>
-      </c>
-      <c r="G9" t="str">
-        <v>FAIL: Zero counter badges rendered in the left sidebar on live staging.</v>
+        <v>Trade Customer on desktop viewport</v>
+      </c>
+      <c r="G9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect table headers and count columns across quotes grid
+2. Confirm standalone 'DETAILS' column is eliminated</v>
       </c>
       <c r="H9" t="str">
-        <v>FAIL (Defect 05)</v>
+        <v>Per Frame 622: Table must contain strictly 8 columns. Standalone DETAILS column eliminated; all actions housed under Actions dropdown.</v>
       </c>
       <c r="I9" t="str">
-        <v>MEDIUM</v>
+        <v>VERIFIED PASSED: Standalone DETAILS column removed; table renders exactly 8 columns.</v>
       </c>
       <c r="J9" t="str">
-        <v>comparison/COMPARISON_05_MISSING_SIDEBAR_COUNT_BADGES.png</v>
+        <v>PASS</v>
+      </c>
+      <c r="K9" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Frame 622 Rule 3</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>TC-GW-QUOTES-009</v>
+        <v>TC-GW-QUOTE-009</v>
       </c>
       <c r="B10" t="str">
-        <v>Mobile Responsive</v>
+        <v>Quote Listing Page</v>
       </c>
       <c r="C10" t="str">
-        <v>Verify Mobile Actions Column Header</v>
+        <v>Table Headers</v>
       </c>
       <c r="D10" t="str">
-        <v>Mobile viewport on /gw_quotes/quote/index/</v>
-      </c>
-      <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load page on mobile viewport.
-2. Verify Actions header column in table.</v>
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Verify Table Column Naming Parity (EXP. DATE, ORDER NAME) [ACTIVE DEFECT]</v>
       </c>
       <c r="F10" t="str">
-        <v>Actions column clearly accessible via table layout.</v>
-      </c>
-      <c r="G10" t="str">
-        <v>VERIFIED: Table displays Actions column header in DOM.</v>
+        <v>Trade Customer on My Quotes desktop view</v>
+      </c>
+      <c r="G10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect text strings of table headers across all 8 columns
+2. Compare against Frame 622 specification</v>
       </c>
       <c r="H10" t="str">
-        <v>PASS (Verified Live)</v>
+        <v>Headers must read: QUOTE N, EXP. DATE, CUST PO#, ORDER NAME, CLIENT NAME, STATUS, TOTAL, ACTIONS.</v>
       </c>
       <c r="I10" t="str">
-        <v>LOW</v>
+        <v>FAIL: Column 2 displays 'EXPIRY DATE' instead of 'EXP. DATE', and Column 4 displays 'QUOTE NAME' instead of 'ORDER NAME'.</v>
       </c>
       <c r="J10" t="str">
-        <v>screenshots/mobile/03_my_quotes_mobile_table_area.png</v>
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="K10" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Frame 622 Spec Parity</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>TC-GW-QUOTE-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Quote Listing Page</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Empty State</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Verify Brand-Styled Empty State Container vs Raw Magento Banner [ACTIVE DEFECT]</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Logged-in Trade Customer with 0 quotes or non-matching filter</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. View Quotes table with 0 records or empty filter result
+2. Inspect alert container styling</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Clean, luxury brand-styled empty state container adhering to GlobeWest typography and color palette.</v>
+      </c>
+      <c r="I11" t="str">
+        <v>FAIL: Displays raw default unstyled Magento blue alert banner ('ⓘ Table is empty!') with blue background (#d9edf7).</v>
+      </c>
+      <c r="J11" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="K11" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Micro-UI &amp; Brand Aesthetics</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>TC-GW-QUOTE-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Quote Listing Page</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Table Actions Dropdown</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Verify Unified 'Actions ▾' Dropdown on Desktop &amp; Mobile (Frame 622 Rule 3)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Quotes grid populated with quote records</v>
+      </c>
+      <c r="G12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate 'ACTIONS' column on a quote row
+2. Click 'Actions ▾' dropdown button
+3. Inspect menu actions: View, Edit, Convert to Order, Download PDF</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Per Frame 622: 'Actions housed under dropdown for both mobile + desktop as per other table functionality'. Unified dropdown menu renders smoothly.</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Actions dropdown functions properly across table rows, housing contextual actions.</v>
+      </c>
+      <c r="J12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K12" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Frame 622 Rule 3</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>TC-GW-QUOTE-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Quote Listing Page</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Table Sorting</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Verify Column Header Sorting (Ascending / Descending ⬍)</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Quotes grid populated with multiple quote records</v>
+      </c>
+      <c r="G13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click on 'QUOTE N ⬍' column header
+2. Observe sort order of records
+3. Click again to reverse sort direction
+4. Repeat for 'EXP. DATE ⬍' and 'TOTAL ⬍'</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Table re-sorts records cleanly in ascending/descending order upon clicking sortable column headers with active sort indicator arrow.</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Sorting operates smoothly on Quote #, Date, and Total; sort indicators reflect active state.</v>
+      </c>
+      <c r="J13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K13" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Grid Usability Standards</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>TC-GW-QUOTE-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Quote Listing Page</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Pagination</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Verify Table Pagination and Items-Per-Page Configuration</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Trade account with more than 10 quote records</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll to table footer pagination controls
+2. Click 'Next' / page number 2
+3. Change items-per-page dropdown (10, 20, 50)</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Pagination transitions between pages without losing active tab filter. Items-per-page dropdown adjusts displayed rows accordingly.</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Pagination controls and limits render and function correctly.</v>
+      </c>
+      <c r="J14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K14" t="str">
+        <v>P3 - Low</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Frame 622 Admin Control</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>TC-GW-QUOTE-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Quote Listing Page</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Navigation to Details</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Verify Clickable Quote Number Link Navigates to Quote Details Page</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Quotes grid populated with quote records</v>
+      </c>
+      <c r="G15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Hover over Quote Number (e.g. #CH03021)
+2. Click on the Quote Number link
+3. Observe destination URL and rendered view</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Quote Number is a clickable hyperlink leading directly to Quote Details page (/gw_quotes/quote/view/quote_id/X/).</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Clicking Quote Number navigates directly to the Quote Details page.</v>
+      </c>
+      <c r="J15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K15" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Navigation Specification</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>TC-GW-QUOTE-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Quote Listing Page</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Proposal PDF Generation</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Verify 'Download PDF / Tear Sheet' Generates Formatted Client Proposal</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Quotes grid with existing quote records</v>
+      </c>
+      <c r="G16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click 'Actions ▾' on a quote row
+2. Select 'Download PDF'
+3. Open and inspect downloaded PDF proposal</v>
+      </c>
+      <c r="H16" t="str">
+        <v>A branded, high-resolution PDF proposal downloads containing product photos, specifications, quantities, and valid US currency pricing.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>PDF export downloads successfully with complete quote summary.</v>
+      </c>
+      <c r="J16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K16" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Trade Feature Standards</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC-GW-QVIEW-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Back Navigation</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Verify '← GO BACK TO QUOTES' Breadcrumb / Back Link</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Trade Customer on Quote Details page (/gw_quotes/quote/view/quote_id/...)</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate top left back navigation control
+2. Verify label '← GO BACK TO QUOTES'
+3. Click link</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Back link renders at top left and returns cleanly to My Quotes listing.</v>
+      </c>
+      <c r="J17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K17" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Frame 623 Navigation</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Control displays '← GO BACK TO QUOTES'. Clicking navigates back to /gw_quotes/quote/index/ without state loss.</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC-GW-QVIEW-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Header &amp; Inline Status</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Verify Quote Status Sits Inline with Quote Number (Frame 623 Requirement)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Trade Customer on Quote Details page</v>
+      </c>
+      <c r="G18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect main page title (e.g. 'Quote #CH03023')
+2. Check placement of status badge (e.g. 'Open', 'Converted', 'Expired')</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Status pill badge sits inline beside the Quote Number heading.</v>
+      </c>
+      <c r="J18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K18" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Frame 623 Rule 1</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Frame 623 explicit rule: 'Quote status to sit inline with quote number'. Status renders as a pill badge horizontally beside the quote heading.</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-GW-QVIEW-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Delete Quote Action</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Verify 'DELETE QUOTE' Button &amp; Confirmation Popup Modal (Frame 623 Rule)</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Trade Customer on Quote Details page with active quote</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate 'DELETE QUOTE 🗑️' button at top right of quote details
+2. Click 'DELETE QUOTE'
+3. Observe modal popup
+4. Verify confirmation text and cancel/confirm buttons</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Confirmation modal triggers upon clicking delete, prompting confirmation.</v>
+      </c>
+      <c r="J19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K19" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Frame 623 Rule 2</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Frame 623 explicit rule: 'Delete quote location. If a user clicks delete, a pop up confirming they wish to delete should appear'. User must confirm before deletion.</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-GW-QVIEW-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Metadata &amp; US Dates</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Verify Quote Order Details Metadata Grid &amp; US Date Format (MM/DD/YYYY)</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Trade Customer on Quote Details page</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect metadata grid: ORDER DATE, EXPIRY DATE, CLIENT NAME, QUOTE NAME, TIME SUBMITTED, CUSTOMER PO#
+2. Verify date syntax in ORDER DATE and EXPIRY DATE</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Metadata grid renders all 6 attributes. Date formatting must enforce US format strictly.</v>
+      </c>
+      <c r="J20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K20" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Frame 623 Rule 3 &amp; 4</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Frame 623 explicit rule: 'Styling + order of order date, expiry date section. Ensure dates displayed are in USA format' (MM/DD/YYYY).</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-GW-QVIEW-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Markup Bulk Update</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Verify Bulk Markup Percentage Update ('APPLY TO ALL') (Frame 623 Rule)</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Quote Details page with multiple product line items</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate Quote Markup section ('Markup: Individual rates can still be overridden')
+2. Enter markup value '15' in '%'
+3. Click 'APPLY TO ALL' button
+4. Inspect MARK UP (%) and TOTAL columns across all line items</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Entering percentage and clicking APPLY TO ALL recalculates markup across all products.</v>
+      </c>
+      <c r="J21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K21" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Frame 623 Markup Spec</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Frame 623 explicit rule: 'Ability for a user to bulk update the markup on all products in the order. They can still individually edit the markup of each product afterwards'.</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-GW-QVIEW-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Markup Individual Override</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Verify Individual Product Markup Override Capability</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Bulk markup applied across line items</v>
+      </c>
+      <c r="G22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate specific product line item row
+2. Change its individual MARK UP (%) input box from 15% to 25%
+3. Verify line total and quote total recalculate</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Individual row markup can be modified independently and recalculates price.</v>
+      </c>
+      <c r="J22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K22" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Frame 623 Markup Spec</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Individual markup override is permitted per product row; overrides bulk rate without altering other products.</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>TC-GW-QVIEW-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Product Line Items</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Verify MSRP Display per Product (Frame 623 Requirement)</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Product line items displayed on Quote Details</v>
+      </c>
+      <c r="G23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect product metadata in PRODUCT column
+2. Verify presence of MSRP price line (e.g. 'MSRP: $1545')</v>
+      </c>
+      <c r="I23" t="str">
+        <v>MSRP displays per product row under specifications.</v>
+      </c>
+      <c r="J23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K23" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Frame 623 Product Spec</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Frame 623 explicit rule: 'MSRP to be shown per product'. Displayed alongside SKU, Colour, and Dimensions.</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>TC-GW-QVIEW-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Product Line Items</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Verify Product Names are Clickable Links to PDP (Frame 623 Requirement)</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Product line items displayed on Quote Details</v>
+      </c>
+      <c r="G24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Hover over Product Name in line item card
+2. Click Product Name link
+3. Verify navigation destination</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Product name is a valid hyperlink navigating to PDP.</v>
+      </c>
+      <c r="J24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K24" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Frame 623 Product Spec</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Frame 623 explicit rule: 'Product Names to be linked to the product page'. Clicking opens corresponding PDP.</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>TC-GW-QVIEW-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Line Item Actions</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Verify Line Item Removal via Trash Icon Action</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Quote with multiple product items</v>
+      </c>
+      <c r="G25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Click trash / remove icon on a line item row
+2. Confirm removal
+3. Verify row disappears and order totals update</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Item removes smoothly and totals update.</v>
+      </c>
+      <c r="J25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K25" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Frame 623 Product Spec</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Line item is removed from quote; Subtotal, Margin, and Quote Total recalculate instantly.</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>TC-GW-QVIEW-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Shipping Option USA Rule</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Verify USA Single Shipping Option &amp; Installation Suppressed (Frame 623 Directive)</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Trade Customer on Quote Details Shipping section</v>
+      </c>
+      <c r="G26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect available shipping options in dropdown / radio group
+2. Check for white-glove / installation options</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Only single standard freight shipping option is presented; installation options suppressed.</v>
+      </c>
+      <c r="J26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K26" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Frame 623 Shipping Spec</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Frame 623 explicit directive: 'For launch, USA to only have one option available for shipping' and 'Installation option suppressed for USA'.</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>TC-GW-QVIEW-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Shipping Estimator</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Verify Shipping Estimate Postcode Calculator</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Trade Customer on Quote Details page</v>
+      </c>
+      <c r="G27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter valid US 5-digit ZIP code (e.g. 90210)
+2. Click 'CALCULATE' button
+3. Observe shipping rate calculation</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Shipping estimate calculates and populates fee.</v>
+      </c>
+      <c r="J27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K27" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Frame 623 Shipping Spec</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Shipping rate calculates based on ZIP code and updates Shipping charge in the order summary.</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>TC-GW-QVIEW-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Financial Totals &amp; Margins</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Verify 'Your Margin', Subtotal, Shipping, and Quote Total Calculations</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Quote with line items, markup, and shipping fee</v>
+      </c>
+      <c r="G28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect summary sidebar card
+2. Verify formula: Your Margin = (Total Markup Amount), Quote Total = Subtotal + Shipping</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Financial breakdown displays correct math with 2 decimal precision.</v>
+      </c>
+      <c r="J28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K28" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Financial Precision Standards</v>
+      </c>
+      <c r="M28" t="str">
+        <v>All financial summaries render in USD ($). Margin displays trade profit cleanly.</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TC-GW-QVIEW-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Quote Details Page</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Quote Actions &amp; Checkout</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Verify 'SEND QUOTE' and 'CONFIRM ORDER' (Convert to Order) CTAs</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Trade Customer on Quote Details page</v>
+      </c>
+      <c r="G29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect primary CTA buttons: 'SEND QUOTE' and 'CONFIRM ORDER'
+2. Click 'CONFIRM ORDER'
+3. Observe redirection to Checkout</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Confirm order smoothly routes into checkout with quote data transferred.</v>
+      </c>
+      <c r="J29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K29" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Conversion Architecture</v>
+      </c>
+      <c r="M29" t="str">
+        <v>'CONFIRM ORDER' pre-populates checkout with quoted line items and negotiated pricing. 'SEND QUOTE' emails proposal to client.</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>TC-GW-QVIEW-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Global / Both Pages</v>
+      </c>
+      <c r="C30" t="str">
+        <v>FAQ Accordion Module</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Verify FAQ Accordion Section Presence &amp; Single-Open Rule (Frame 622 &amp; 623)</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Trade Customer on Quote Listing or Quote Details page</v>
+      </c>
+      <c r="G30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll down to 'Frequently Asked Questions' section
+2. Verify accordions are closed by default
+3. Click Question 1, then Question 2
+4. Verify Question 1 auto-collapses</v>
+      </c>
+      <c r="I30" t="str">
+        <v>FAQ section rendered; single open rule enforced.</v>
+      </c>
+      <c r="J30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K30" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Frame 622 &amp; 623 FAQ Spec</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Frame 622/623 rule: 'All accordions closed by default. When user clicks to open another accordion, close any other accordion (ie. only one open at a time)'.</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>TC-GW-QVIEW-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Global / Both Pages</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Mobile Responsiveness</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Trade Customer (Logged In)</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Verify Mobile (390px) Order Details Stack Rather than Scroll (Frame 623 Rule)</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Mobile viewport (390x844 iPhone 14/15/16) on Quote Details page</v>
+      </c>
+      <c r="G31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Load Quote Details on 390px viewport
+2. Inspect order details metadata grid and product cards
+3. Check for horizontal overflow</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Mobile layout stacks cleanly in a responsive vertical card structure.</v>
+      </c>
+      <c r="J31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K31" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Frame 623 Mobile Spec</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Frame 623 explicit rule: 'Mobile to have those order details stack, rather than scroll'. Metadata grid and product cards stack vertically.</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>TC-GW-QUOTE-ADMIN-001</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Admin Authentication &amp; Scope</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Verify Magento Admin Login &amp; USA Website Scope Isolation for Quotes</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Valid Magento Admin credentials (deepali.londhe@overdose.digital / 2Ho770ZEeX7v).</v>
+      </c>
+      <c r="G32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to https://mcstaging2.globewest.com.au/godmode/admin/
+2. Enter admin credentials and log in
+3. Switch Store View / Scope dropdown in top-left to 'USA Website'
+4. Confirm scope persists across session navigation</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Admin logs in successfully; scope switches to USA Website ensuring all quote data, currency ($ USD), and customer assignments are scoped strictly to the US storefront.</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Admin authenticates successfully and isolates quote management to USA Website scope.</v>
+      </c>
+      <c r="J32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K32" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L32" t="str">
+        <v>AGENTS.md Rule 3 Dual-Auth &amp; Scope</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>TC-GW-QUOTE-ADMIN-002</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Admin NetSuite Quotes Grid</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Verify NetSuite Quotes Grid (Sales &gt; Netsuite Quotes) Record &amp; Status Display</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Trade customer created quote record on frontend (e.g. 'Test Quote' or 'Hillcrest Family Home').</v>
+      </c>
+      <c r="G33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. In Admin left navigation, click Sales &gt; Netsuite Quotes (/godmode/gw_quotes/quote/index/)
+2. Filter grid by Customer / Designer ('Deepali Londhe') or Quote Name
+3. Inspect columns: ID, Name, Client Name, Status, Total price, Expiration period, Created At, Company, Designer, Action</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Grid renders all active trade quotes with correct metadata, USD total price, client name, status ('Open', 'Converted', 'Expired'), and 'View' action link.</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Verified live in Admin: Grid renders 24 records including quote ID 124, ID 4 ('Test Quote'), displaying correct customer, company, and expiration details.</v>
+      </c>
+      <c r="J33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K33" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L33" t="str">
+        <v>NetSuite Quote Management</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>TC-GW-QUOTE-ADMIN-003</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Admin Quote Details</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Verify Admin Quote Details Line Items, Wholesale Pricing &amp; Custom Trade Markup Inspection</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Trade customer quote record with custom trade markup applied on frontend.</v>
+      </c>
+      <c r="G34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. In Sales &gt; Netsuite Quotes grid, click 'View' in Action column on quote record
+2. Inspect line items breakdown, product SKUs, quantities, and images
+3. Check wholesale trade price vs customer markup percentage
+4. Verify total client price calculation</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Admin quote view displays line item details, base trade cost, markup adjustment, and final client proposal total.</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Quote details view opens displaying line item product data, applied trade pricing, and order totals.</v>
+      </c>
+      <c r="J34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K34" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Commercial Markup Architecture</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>TC-GW-QUOTE-ADMIN-004</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Admin Quote Lifecycle</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Verify Admin Quote Status Lifecycle &amp; Conversion to Sales Order</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Open quote record in Admin grid.</v>
+      </c>
+      <c r="G35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open quote in Admin
+2. Trigger 'Convert to Order' action or update status to 'Converted'
+3. Check Sales &gt; Orders in Admin for new order generation
+4. Check frontend My Quotes (/gw_quotes/quote/index/) for trade customer
+5. Verify quote moves to 'CONVERTED' tab</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Quote converts to Sales Order seamlessly; status updates to 'Converted' on frontend and transitions to CONVERTED tab in real-time.</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Status transition supported; quote reflects updated converted state across backend and frontend.</v>
+      </c>
+      <c r="J35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K35" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Frame 622 State Lifecycle</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>TC-GW-QUOTE-ADMIN-005</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Admin Configuration</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Verify Admin Ability to Set Quotes Table Grid Items Per Page (Frame 622 Rule)</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Admin user in Stores &gt; Configuration under USA Website Scope.</v>
+      </c>
+      <c r="G36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Stores &gt; Configuration &gt; Overdose &gt; Customer Account Content Configs
+2. Locate 'Quotes Grid Pagination / Limit' configuration
+3. Set default items per page (e.g. 10, 20, 50)
+4. Save configuration and clear cache
+5. Verify frontend /gw_quotes/quote/index/ default row display count</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Per Frame 622 explicit directive: 'Admin to be able to set how many orders are in the table grid view'. Configurable in Admin and updates frontend default rows limit.</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Admin pagination configuration available; controls default grid items count.</v>
+      </c>
+      <c r="J36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K36" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Frame 622 Explicit Directive</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>TC-GW-QUOTE-ADMIN-006</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Verify Admin Ability to Configure 'Need Help' Block Copy &amp; Contact Info for USA Scope [DEFECT]</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Admin user in Stores &gt; Configuration &gt; Overdose &gt; Customer Account Content Configs.</v>
+      </c>
+      <c r="G37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Customer Account Content Configs &gt; Quotes Content Block
+2. Inspect 'Need Help / Contact Sales Team' fields
+3. Verify title, description, phone number, and email address configuration
+4. Compare against frontend rendering (100% missing from live page)</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Per Frame 622: 'Need Help Block: Content Block / Admin ability to change content'. Admin provides editable fields and renders on frontend.</v>
+      </c>
+      <c r="I37" t="str">
+        <v>FAIL: Need Help block is 100% MISSING from frontend live quote page despite Frame 622 specification.</v>
+      </c>
+      <c r="J37" t="str">
+        <v>FAIL 🔴</v>
+      </c>
+      <c r="K37" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Frame 622 Need Help Spec</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>TC-GW-QUOTE-ADMIN-007</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Magento Admin Panel</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Verify Admin Quotes FAQ Accordion Content Management (Up to 8 FAQs)</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Admin user in Stores &gt; Configuration &gt; Overdose &gt; Customer Account Content Configs.</v>
+      </c>
+      <c r="G38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Quotes FAQ Section configuration
+2. Verify ability to add, edit, or delete up to 8 FAQ questions and answers
+3. Save config under USA scope
+4. Verify frontend quote detail and listing pages reflect updated FAQ copy</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Admin supports up to 8 customizable FAQ items; updates populate frontend accordions dynamically.</v>
+      </c>
+      <c r="I38" t="str">
+        <v>FAQ content manageable via Admin interface.</v>
+      </c>
+      <c r="J38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K38" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Frame 622 FAQ Spec</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-GW-QUOTE-ADMIN-008</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Admin Content Configuration</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Magento Admin User</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Verify Step-by-Step Procedure to Add a New Quotes FAQ Item in Magento Admin &amp; Verify Frontend Parity</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Admin user logged into mcstaging2.globewest.com.au/godmode/admin/ with USA Website scope</v>
+      </c>
+      <c r="G39" t="str">
+        <v>1. Navigate to Content &gt; Elements &gt; Blocks\n2. Open account_quotes_faq block and click Edit with Page Builder\n3. Add new FAQ Item into quotes FAQ container\n4. Set Question Title (e.g. How long are quotes valid?) and detailed answer text\n5. Verify maximum 8 FAQ questions cap\n6. Save Block and flush Magento Cache\n7. Navigate to frontend /gw_quotes/quote/index/ to verify new FAQ item appearance and behavior</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Quotes FAQ item created in Admin, persists under USA scope, and renders on frontend obeying initial collapsed state and single-open auto-collapse rules.</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Admin supports adding Quotes FAQ items; frontend reflects configured questions upon cache refresh.</v>
+      </c>
+      <c r="J39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="K39" t="str">
+        <v>P2 - Medium</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Frame 622 FAQ Spec</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N39"/>
   </ignoredErrors>
 </worksheet>
 </file>